--- a/import/schedule/Корректировка.xlsx
+++ b/import/schedule/Корректировка.xlsx
@@ -121,9 +121,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -514,7 +513,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Times New Roman" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -549,7 +548,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Times New Roman" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
